--- a/frontend/huongvantra-web-client/public/templates/FileMau_YeuCauTaoHangHoaMoi.xlsx
+++ b/frontend/huongvantra-web-client/public/templates/FileMau_YeuCauTaoHangHoaMoi.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1">'1_SanPham'!A3:F16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2">'2_SKU'!A3:M26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2">'2_SKU'!A3:M25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3">'3_ThuocTinh'!A3:C19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4">'4_BOM'!A3:E22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5">'_ThamChieu'!A3:E11</definedName>
@@ -694,7 +694,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A25"/>
+  <dimension ref="A1:A29"/>
   <cols>
     <col min="1" max="1" width="102.83203125" customWidth="1"/>
   </cols>
@@ -756,7 +756,7 @@
     </row>
     <row r="12" ht="18" customHeight="1">
       <c s="21" r="A12" t="str">
-        <v>6. Ảnh sản phẩm: thêm sau khi import bằng nút Thêm ảnh trên web (upload local).</v>
+        <v>6. Ảnh sản phẩm: nén Excel + ảnh vào ZIP. Ảnh được ghép theo Mã sản phẩm và upload Cloudinary khi gửi duyệt.</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -776,57 +776,77 @@
     </row>
     <row r="16" ht="18" customHeight="1">
       <c s="21" r="A16" t="str">
-        <v>• Mỗi sản phẩm chỉ có đúng 1 đơn vị cơ bản = Có, Quy đổi = 1.</v>
+        <v>• ZIP chỉ có 1 file .xlsx; ảnh theo Mã sản phẩm, ví dụ HVT01.jpg, HVT01_2.jpg (tối đa 5 ảnh/SP, 5MB/ảnh).</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c s="21" r="A17" t="str">
-        <v>• Đơn vị tồn: Piece hoặc Gram.</v>
+        <v>• Phải cấu hình Cloudinary trước khi gửi duyệt file có ảnh. Không dùng URL ảnh trực tiếp từ website làm dữ liệu lâu dài.</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c s="21" r="A18" t="str">
-        <v>• Loại hàng hóa: THANH_PHAM / NGUYEN_LIEU / BAO_BI.</v>
+        <v>• Giá vốn trong file Hương Vân chỉ là dữ liệu demo (~50% giá bán), không phải giá vốn thực tế của HTX.</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c s="21" r="A19" t="str">
-        <v>• Cột Có/Không chỉ nhận: Có hoặc Không.</v>
+        <v>• Mỗi sản phẩm chỉ có đúng 1 đơn vị cơ bản = Có, Quy đổi = 1.</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c s="21" r="A20" t="str">
-        <v>• Không xóa dòng tiêu đề cột. Dòng bắt đầu bằng ▼ là dòng trang trí (không import).</v>
+        <v>• Quy đổi phải là số nguyên dương; giá SKU quy đổi luôn = giá SKU cơ bản × Quy đổi.</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c s="21" r="A21" t="str">
-        <v/>
+        <v>• Đơn vị tồn: Piece hoặc Gram.</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c s="21" r="A22" t="str">
+        <v>• Loại hàng hóa: THANH_PHAM / NGUYEN_LIEU / BAO_BI.</v>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c s="21" r="A23" t="str">
+        <v>• Cột Có/Không chỉ nhận: Có hoặc Không.</v>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c s="21" r="A24" t="str">
+        <v>• Không xóa dòng tiêu đề cột. Dòng bắt đầu bằng ▼ là dòng trang trí (không import).</v>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c s="21" r="A25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c s="21" r="A26" t="str">
         <v>Mẹo đọc file</v>
       </c>
     </row>
-    <row r="23" ht="24" customHeight="1">
-      <c s="21" r="A23" t="str">
+    <row r="27" ht="24" customHeight="1">
+      <c s="21" r="A27" t="str">
         <v>• Header màu đậm = tiêu đề cột (giữ nguyên).</v>
       </c>
     </row>
-    <row r="24" ht="24" customHeight="1">
-      <c s="21" r="A24" t="str">
+    <row r="28" ht="24" customHeight="1">
+      <c s="21" r="A28" t="str">
         <v>• Sheet BOM / SKU / Thuộc tính: mỗi sản phẩm một khối màu, cách nhau bằng dòng trống.</v>
       </c>
     </row>
-    <row r="25" ht="24" customHeight="1">
-      <c s="21" r="A25" t="str">
+    <row r="29" ht="24" customHeight="1">
+      <c s="21" r="A29" t="str">
         <v>• Giá trước thuế / Giá vốn format số. Thuế % để trống = 0. SKU quy đổi tự nhân giá đơn vị cơ bản.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A25"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A29"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -836,11 +856,11 @@
   <dimension ref="A1:F16"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
-    <col min="2" max="2" width="21.83203125" customWidth="1"/>
+    <col min="2" max="2" width="23.83203125" customWidth="1"/>
     <col min="3" max="3" width="16.83203125" customWidth="1"/>
     <col min="4" max="4" width="20.83203125" customWidth="1"/>
     <col min="5" max="5" width="14.83203125" customWidth="1"/>
-    <col min="6" max="6" width="34.83203125" customWidth="1"/>
+    <col min="6" max="6" width="36.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -903,24 +923,24 @@
         <v>Mô tả</v>
       </c>
     </row>
-    <row r="4" ht="18" customHeight="1">
+    <row r="4" ht="30" customHeight="1">
       <c s="13" r="A4" t="str">
-        <v>SP01</v>
+        <v>HVT07</v>
       </c>
       <c s="13" r="B4" t="str">
-        <v>Trà Sen</v>
+        <v>Hương Trà Hương Vân</v>
       </c>
       <c s="13" r="C4" t="str">
         <v>THANH_PHAM</v>
       </c>
       <c s="13" r="D4" t="str">
-        <v>Trà</v>
+        <v>Trà xanh Tân Cương Thái Nguyên</v>
       </c>
       <c s="13" r="E4" t="str">
         <v>Piece</v>
       </c>
       <c s="13" r="F4" t="str">
-        <v>Ví dụ nhẹ — xóa nếu không dùng</v>
+        <v>Ví dụ theo catalog Hương Vân — xóa nếu không dùng</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
@@ -1177,12 +1197,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M25"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="14.83203125" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" customWidth="1"/>
+    <col min="3" max="3" width="20.83203125" customWidth="1"/>
+    <col min="4" max="4" width="11.83203125" customWidth="1"/>
     <col min="5" max="5" width="10.83203125" customWidth="1"/>
     <col min="6" max="6" width="12.83203125" customWidth="1"/>
     <col min="7" max="7" width="16.83203125" customWidth="1"/>
@@ -1319,7 +1339,7 @@
     </row>
     <row r="4" ht="22" customHeight="1">
       <c s="13" r="A4" t="str">
-        <v>▼ SP01  —  Trà Sen</v>
+        <v>▼ HVT07  —  Hương Trà Hương Vân</v>
       </c>
       <c s="13" r="B4" t="str">
         <v/>
@@ -1360,16 +1380,16 @@
     </row>
     <row r="5" ht="18" customHeight="1">
       <c s="13" r="A5" t="str">
-        <v>SP01</v>
+        <v>HVT07</v>
       </c>
       <c s="13" r="B5" t="str">
-        <v>SP01-U1</v>
+        <v>HVT07-U1</v>
       </c>
       <c s="13" r="C5" t="str">
-        <v>TRA-SEN-LY</v>
+        <v>HVT-HUONGTRA-100G</v>
       </c>
       <c s="13" r="D5" t="str">
-        <v>Ly</v>
+        <v>Hộp 100g</v>
       </c>
       <c s="13" r="E5">
         <v>1</v>
@@ -1378,13 +1398,13 @@
         <v>Có</v>
       </c>
       <c s="13" r="G5">
-        <v>35000</v>
+        <v>175000</v>
       </c>
       <c s="13" r="H5" t="str">
         <v/>
       </c>
       <c s="13" r="I5">
-        <v>12000</v>
+        <v>87500</v>
       </c>
       <c s="13" r="J5" t="str">
         <v/>
@@ -1393,56 +1413,56 @@
         <v>Có</v>
       </c>
       <c s="13" r="L5">
-        <v>0</v>
-      </c>
-      <c s="13" r="M5" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1">
+        <v>5</v>
+      </c>
+      <c s="13" r="M5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" ht="10" customHeight="1">
       <c s="13" r="A6" t="str">
-        <v>SP01</v>
+        <v/>
       </c>
       <c s="13" r="B6" t="str">
-        <v>SP01-U2</v>
+        <v/>
       </c>
       <c s="13" r="C6" t="str">
-        <v>TRA-SEN-SET</v>
+        <v/>
       </c>
       <c s="13" r="D6" t="str">
-        <v>Set</v>
-      </c>
-      <c s="13" r="E6">
-        <v>2</v>
+        <v/>
+      </c>
+      <c s="13" r="E6" t="str">
+        <v/>
       </c>
       <c s="13" r="F6" t="str">
-        <v>Không</v>
-      </c>
-      <c s="13" r="G6">
-        <v>70000</v>
+        <v/>
+      </c>
+      <c s="13" r="G6" t="str">
+        <v/>
       </c>
       <c s="13" r="H6" t="str">
         <v/>
       </c>
-      <c s="13" r="I6">
-        <v>24000</v>
+      <c s="13" r="I6" t="str">
+        <v/>
       </c>
       <c s="13" r="J6" t="str">
         <v/>
       </c>
       <c s="13" r="K6" t="str">
-        <v>Có</v>
-      </c>
-      <c s="13" r="L6">
-        <v>0</v>
+        <v/>
+      </c>
+      <c s="13" r="L6" t="str">
+        <v/>
       </c>
       <c s="13" r="M6" t="str">
         <v/>
       </c>
     </row>
-    <row r="7" ht="10" customHeight="1">
+    <row r="7" ht="22" customHeight="1">
       <c s="13" r="A7" t="str">
-        <v/>
+        <v>▼ (thêm sản phẩm mới bên dưới)</v>
       </c>
       <c s="13" r="B7" t="str">
         <v/>
@@ -1481,9 +1501,9 @@
         <v/>
       </c>
     </row>
-    <row r="8" ht="22" customHeight="1">
+    <row r="8" ht="18" customHeight="1">
       <c s="13" r="A8" t="str">
-        <v>▼ (thêm sản phẩm mới bên dưới)</v>
+        <v/>
       </c>
       <c s="13" r="B8" t="str">
         <v/>
@@ -2219,57 +2239,16 @@
         <v/>
       </c>
     </row>
-    <row r="26" ht="18" customHeight="1">
-      <c s="13" r="A26" t="str">
-        <v/>
-      </c>
-      <c s="13" r="B26" t="str">
-        <v/>
-      </c>
-      <c s="13" r="C26" t="str">
-        <v/>
-      </c>
-      <c s="13" r="D26" t="str">
-        <v/>
-      </c>
-      <c s="13" r="E26" t="str">
-        <v/>
-      </c>
-      <c s="13" r="F26" t="str">
-        <v/>
-      </c>
-      <c s="13" r="G26" t="str">
-        <v/>
-      </c>
-      <c s="13" r="H26" t="str">
-        <v/>
-      </c>
-      <c s="13" r="I26" t="str">
-        <v/>
-      </c>
-      <c s="13" r="J26" t="str">
-        <v/>
-      </c>
-      <c s="13" r="K26" t="str">
-        <v/>
-      </c>
-      <c s="13" r="L26" t="str">
-        <v/>
-      </c>
-      <c s="13" r="M26" t="str">
-        <v/>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A3:M26"/>
+  <autoFilter ref="A3:M25"/>
   <mergeCells count="4">
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="A4:M4"/>
-    <mergeCell ref="A8:M8"/>
+    <mergeCell ref="A7:M7"/>
   </mergeCells>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M26"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M25"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2318,7 +2297,7 @@
     </row>
     <row r="4" ht="22" customHeight="1">
       <c s="13" r="A4" t="str">
-        <v>▼ SP01  —  Trà Sen</v>
+        <v>▼ HVT07  —  Hương Trà Hương Vân</v>
       </c>
       <c s="13" r="B4" t="str">
         <v/>
@@ -2329,13 +2308,13 @@
     </row>
     <row r="5" ht="18" customHeight="1">
       <c s="13" r="A5" t="str">
-        <v>SP01</v>
+        <v>HVT07</v>
       </c>
       <c s="13" r="B5" t="str">
-        <v>Size</v>
+        <v>Xuất xứ</v>
       </c>
       <c s="13" r="C5" t="str">
-        <v>M</v>
+        <v>Thái Nguyên</v>
       </c>
     </row>
     <row r="6" ht="10" customHeight="1">
@@ -2514,7 +2493,7 @@
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
     <col min="3" max="3" width="24.83203125" customWidth="1"/>
     <col min="4" max="4" width="12.83203125" customWidth="1"/>
-    <col min="5" max="5" width="43.83203125" customWidth="1"/>
+    <col min="5" max="5" width="44.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -2570,7 +2549,7 @@
     </row>
     <row r="4" ht="22" customHeight="1">
       <c s="13" r="A4" t="str">
-        <v>▼ SP01  —  Trà Sen</v>
+        <v>▼ HVT07  —  Hương Trà Hương Vân</v>
       </c>
       <c s="13" r="B4" t="str">
         <v/>
@@ -2585,21 +2564,21 @@
         <v/>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1">
+    <row r="5" ht="30" customHeight="1">
       <c s="13" r="A5" t="str">
-        <v>SP01</v>
+        <v>HVT07</v>
       </c>
       <c s="13" r="B5" t="str">
-        <v>SP01-U1</v>
+        <v>HVT07-U1</v>
       </c>
       <c s="13" r="C5" t="str">
-        <v>LA-TRA-SEN-G</v>
+        <v>NL-TRA-XANH-G</v>
       </c>
       <c s="13" r="D5">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c s="13" r="E5" t="str">
-        <v>Ví dụ BOM — Sản phẩm kệ bắt buộc có BOM</v>
+        <v>Ví dụ BOM — cần import nguyên liệu cùng file hoặc đã có sẵn</v>
       </c>
     </row>
     <row r="6" ht="10" customHeight="1">
@@ -2911,8 +2890,8 @@
   <cols>
     <col min="1" max="1" width="17.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="17.83203125" customWidth="1"/>
-    <col min="4" max="4" width="37.83203125" customWidth="1"/>
+    <col min="3" max="3" width="34.83203125" customWidth="1"/>
+    <col min="4" max="4" width="42.83203125" customWidth="1"/>
     <col min="5" max="5" width="24.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2967,7 +2946,7 @@
         <v>TÊN THUỘC TÍNH GỢI Ý</v>
       </c>
     </row>
-    <row r="4" ht="18" customHeight="1">
+    <row r="4" ht="30" customHeight="1">
       <c s="13" r="A4" t="str">
         <v>THANH_PHAM</v>
       </c>
@@ -2975,16 +2954,16 @@
         <v>Piece</v>
       </c>
       <c s="13" r="C4" t="str">
-        <v>Trà</v>
+        <v>Trà xanh Tân Cương Thái Nguyên</v>
       </c>
       <c s="13" r="D4" t="str">
-        <v>LA-TRA-SEN-G — Lá trà sen — g</v>
+        <v>NL-TRA-XANH-G — Trà xanh thô Tân Cương — g</v>
       </c>
       <c s="13" r="E4" t="str">
         <v>Hương vị</v>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1">
+    <row r="5" ht="30" customHeight="1">
       <c s="13" r="A5" t="str">
         <v>NGUYEN_LIEU</v>
       </c>
@@ -2992,16 +2971,16 @@
         <v>Gram</v>
       </c>
       <c s="13" r="C5" t="str">
-        <v>Trà</v>
+        <v>Set Quà Cao Cấp</v>
       </c>
       <c s="13" r="D5" t="str">
-        <v>LY-GIAY-350 — Ly giấy 350ml — Cái</v>
+        <v>NL-HONG-TRA-G — Hồng trà thô Hương Vân — g</v>
       </c>
       <c s="13" r="E5" t="str">
-        <v>Size</v>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1">
+        <v>Xuất xứ</v>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
       <c s="13" r="A6" t="str">
         <v>BAO_BI</v>
       </c>
@@ -3009,13 +2988,13 @@
         <v/>
       </c>
       <c s="13" r="C6" t="str">
-        <v>Trà</v>
+        <v>Kẹo Trà</v>
       </c>
       <c s="13" r="D6" t="str">
-        <v/>
+        <v>BB-HOP-GIAY-HVT — Hộp giấy Hương Vân — Cái</v>
       </c>
       <c s="13" r="E6" t="str">
-        <v>Dung tích</v>
+        <v>Đóng gói</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -3026,7 +3005,7 @@
         <v/>
       </c>
       <c s="13" r="C7" t="str">
-        <v/>
+        <v>Dụng Cụ Trà</v>
       </c>
       <c s="13" r="D7" t="str">
         <v/>
@@ -3043,7 +3022,7 @@
         <v/>
       </c>
       <c s="13" r="C8" t="str">
-        <v/>
+        <v>Hoa Trà Sáng Tạo</v>
       </c>
       <c s="13" r="D8" t="str">
         <v/>
@@ -3060,12 +3039,29 @@
         <v/>
       </c>
       <c s="13" r="C9" t="str">
-        <v/>
+        <v>Trà nguyên liệu</v>
       </c>
       <c s="13" r="D9" t="str">
         <v/>
       </c>
       <c s="13" r="E9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c s="13" r="A10" t="str">
+        <v/>
+      </c>
+      <c s="13" r="B10" t="str">
+        <v/>
+      </c>
+      <c s="13" r="C10" t="str">
+        <v>Bao bì sản xuất</v>
+      </c>
+      <c s="13" r="D10" t="str">
+        <v/>
+      </c>
+      <c s="13" r="E10" t="str">
         <v/>
       </c>
     </row>
